--- a/02_Groups/Muscle_size/c_data/clustering.xlsx
+++ b/02_Groups/Muscle_size/c_data/clustering.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="277">
   <si>
     <t>sheet</t>
   </si>
@@ -596,12 +596,6 @@
   </si>
   <si>
     <t>0.5.9</t>
-  </si>
-  <si>
-    <t>htmlwidgets</t>
-  </si>
-  <si>
-    <t>1.6.4</t>
   </si>
   <si>
     <t>IRanges</t>
@@ -1292,7 +1286,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -1677,7 +1671,7 @@
         <v>192</v>
       </c>
       <c r="C35" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -1688,7 +1682,7 @@
         <v>194</v>
       </c>
       <c r="C36" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1751,7 +1745,7 @@
         <v>205</v>
       </c>
       <c r="B42" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="C42" t="s">
         <v>129</v>
@@ -1759,10 +1753,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>206</v>
+      </c>
+      <c r="B43" t="s">
         <v>207</v>
-      </c>
-      <c r="B43" t="s">
-        <v>163</v>
       </c>
       <c r="C43" t="s">
         <v>129</v>
@@ -1798,7 +1792,7 @@
         <v>213</v>
       </c>
       <c r="C46" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1809,7 +1803,7 @@
         <v>215</v>
       </c>
       <c r="C47" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1952,7 +1946,7 @@
         <v>241</v>
       </c>
       <c r="C60" t="s">
-        <v>129</v>
+        <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1963,7 +1957,7 @@
         <v>243</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1996,7 +1990,7 @@
         <v>249</v>
       </c>
       <c r="C64" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -2007,7 +2001,7 @@
         <v>251</v>
       </c>
       <c r="C65" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -2070,7 +2064,7 @@
         <v>262</v>
       </c>
       <c r="B71" t="s">
-        <v>263</v>
+        <v>161</v>
       </c>
       <c r="C71" t="s">
         <v>129</v>
@@ -2078,10 +2072,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>263</v>
+      </c>
+      <c r="B72" t="s">
         <v>264</v>
-      </c>
-      <c r="B72" t="s">
-        <v>161</v>
       </c>
       <c r="C72" t="s">
         <v>129</v>
@@ -2150,17 +2144,6 @@
         <v>276</v>
       </c>
       <c r="C78" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
-        <v>277</v>
-      </c>
-      <c r="B79" t="s">
-        <v>278</v>
-      </c>
-      <c r="C79" t="s">
         <v>129</v>
       </c>
     </row>

--- a/02_Groups/Muscle_size/c_data/clustering.xlsx
+++ b/02_Groups/Muscle_size/c_data/clustering.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="275">
   <si>
     <t>sheet</t>
   </si>
@@ -64,7 +64,7 @@
     <t>space</t>
   </si>
   <si>
-    <t>Per subject: HR/LR arm, group, cluster, and PC1 and PC2 of the scaled traits.</t>
+    <t>Per subject: HR/LR, group, cluster, and PC1 and PC2 of the scaled traits.</t>
   </si>
   <si>
     <t>space_variance</t>
@@ -235,16 +235,16 @@
     <t>k3</t>
   </si>
   <si>
-    <t>arm</t>
-  </si>
-  <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
+    <t>hr_lr</t>
+  </si>
+  <si>
+    <t>The study's HR or LR label, shown beside a cluster grouping's own group.</t>
   </si>
   <si>
     <t>group</t>
   </si>
   <si>
-    <t>Group the row belongs to (HR, LR, Hi, Lo, C1, C2), or a group cell such as HR_T1.</t>
+    <t>Group the row belongs to: HR or LR, or C1 or C2 in a proteome grouping.</t>
   </si>
   <si>
     <t>PC1</t>
@@ -379,22 +379,16 @@
     <t>HR</t>
   </si>
   <si>
-    <t>Hi</t>
-  </si>
-  <si>
     <t>LR</t>
   </si>
   <si>
-    <t>Lo</t>
-  </si>
-  <si>
     <t>phenotype</t>
   </si>
   <si>
     <t>00_Setup/Input/phenotype.csv</t>
   </si>
   <si>
-    <t>5a1989db406daa0b70189a9f0df52cf3</t>
+    <t>cdb8d908fb24ab0d2be6f2d00021db81</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -1302,90 +1296,90 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
         <v>124</v>
-      </c>
-      <c r="B2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -1393,758 +1387,758 @@
         <v>58</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B13" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C13" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B14" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B15" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" t="s">
         <v>151</v>
-      </c>
-      <c r="B15" t="s">
-        <v>152</v>
-      </c>
-      <c r="C15" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C16" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C21" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B22" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C24" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B26" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C26" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B27" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B28" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B30" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B31" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C31" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B32" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C32" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C33" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B34" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B36" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B37" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C37" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:3">
       <c r="A38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C39" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B41" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B42" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C42" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C43" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B44" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C44" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C45" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B46" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C46" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B47" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C47" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B48" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C48" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B49" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B50" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C50" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B51" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C51" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B52" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B53" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C53" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B54" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C54" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B55" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C55" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B56" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C56" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B57" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C57" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B58" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C58" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B59" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C59" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B60" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C60" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B61" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C61" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B62" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C62" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B63" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C63" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B64" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C64" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B65" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C65" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B66" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C66" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B67" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C67" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B68" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C68" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B69" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C69" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B71" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C71" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B72" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C72" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B73" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C73" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B74" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C74" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B75" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C75" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B76" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C76" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B77" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C77" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B78" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C78" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -3392,7 +3386,7 @@
         <v>117</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2">
         <v>-0.9200264013847459</v>
@@ -3412,7 +3406,7 @@
         <v>117</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D3">
         <v>-2.566276486720809</v>
@@ -3432,7 +3426,7 @@
         <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4">
         <v>-2.26960860624147</v>
@@ -3452,7 +3446,7 @@
         <v>117</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D5">
         <v>-0.5212818663289102</v>
@@ -3472,7 +3466,7 @@
         <v>117</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D6">
         <v>-1.629890077810509</v>
@@ -3492,7 +3486,7 @@
         <v>117</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D7">
         <v>-1.765890108124135</v>
@@ -3512,7 +3506,7 @@
         <v>117</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D8">
         <v>-1.104128876417801</v>
@@ -3532,7 +3526,7 @@
         <v>117</v>
       </c>
       <c r="C9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D9">
         <v>0.1490895154510403</v>
@@ -3549,10 +3543,10 @@
         <v>109</v>
       </c>
       <c r="B10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D10">
         <v>0.2486335312160351</v>
@@ -3569,10 +3563,10 @@
         <v>110</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D11">
         <v>-0.8213747445579055</v>
@@ -3589,10 +3583,10 @@
         <v>111</v>
       </c>
       <c r="B12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D12">
         <v>1.588076749679427</v>
@@ -3609,10 +3603,10 @@
         <v>112</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D13">
         <v>0.6569063970243449</v>
@@ -3629,10 +3623,10 @@
         <v>113</v>
       </c>
       <c r="B14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D14">
         <v>2.47858739522493</v>
@@ -3649,10 +3643,10 @@
         <v>114</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D15">
         <v>1.946936877902724</v>
@@ -3669,10 +3663,10 @@
         <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D16">
         <v>2.805905773949406</v>
@@ -3689,10 +3683,10 @@
         <v>116</v>
       </c>
       <c r="B17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D17">
         <v>1.72434092713838</v>
@@ -3761,13 +3755,13 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" t="s">
         <v>121</v>
-      </c>
-      <c r="B2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
